--- a/PLANTILLA_IMPORTACION_SUMINISTROS_SKILLED.xlsx
+++ b/PLANTILLA_IMPORTACION_SUMINISTROS_SKILLED.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Suministros" sheetId="1" r:id="Rc98f996cf3af4621"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Suministros" sheetId="1" r:id="Rd2bba6b0c5234865"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -352,18 +352,17 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="31" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="29" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="19" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="19" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="25" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="16" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="34" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="17" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="17" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="36" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -380,27 +379,24 @@
         <x:v>Marca</x:v>
       </x:c>
       <x:c r="E1" s="19" t="str">
-        <x:v>Código de marca / modelo</x:v>
+        <x:v>Ubicación</x:v>
       </x:c>
       <x:c r="F1" s="19" t="str">
-        <x:v>Ubicación</x:v>
+        <x:v>Unidad</x:v>
       </x:c>
       <x:c r="G1" s="19" t="str">
-        <x:v>Unidad</x:v>
+        <x:v>Stock Inicial</x:v>
       </x:c>
       <x:c r="H1" s="19" t="str">
-        <x:v>Stock Inicial</x:v>
+        <x:v>Stock Mínimo</x:v>
       </x:c>
       <x:c r="I1" s="19" t="str">
-        <x:v>Stock Mínimo</x:v>
+        <x:v>Precio Unitario</x:v>
       </x:c>
       <x:c r="J1" s="19" t="str">
-        <x:v>Precio Unitario</x:v>
-      </x:c>
-      <x:c r="K1" s="19" t="str">
         <x:v>Moneda del costo</x:v>
       </x:c>
-      <x:c r="L1" s="20" t="str">
+      <x:c r="K1" s="20" t="str">
         <x:v>URL Imagen (opcional)</x:v>
       </x:c>
     </x:row>
@@ -411,12 +407,11 @@
       <x:c r="D2" s="12" t="str"/>
       <x:c r="E2" s="12" t="str"/>
       <x:c r="F2" s="12" t="str"/>
-      <x:c r="G2" s="12" t="str"/>
+      <x:c r="G2" s="14" t="str"/>
       <x:c r="H2" s="14" t="str"/>
-      <x:c r="I2" s="14" t="str"/>
-      <x:c r="J2" s="16" t="str"/>
-      <x:c r="K2" s="12" t="str"/>
-      <x:c r="L2" s="22" t="str"/>
+      <x:c r="I2" s="16" t="str"/>
+      <x:c r="J2" s="12" t="str"/>
+      <x:c r="K2" s="22" t="str"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="21" t="str"/>
@@ -425,12 +420,11 @@
       <x:c r="D3" s="12" t="str"/>
       <x:c r="E3" s="12" t="str"/>
       <x:c r="F3" s="12" t="str"/>
-      <x:c r="G3" s="12" t="str"/>
+      <x:c r="G3" s="14" t="str"/>
       <x:c r="H3" s="14" t="str"/>
-      <x:c r="I3" s="14" t="str"/>
-      <x:c r="J3" s="16" t="str"/>
-      <x:c r="K3" s="12" t="str"/>
-      <x:c r="L3" s="22" t="str"/>
+      <x:c r="I3" s="16" t="str"/>
+      <x:c r="J3" s="12" t="str"/>
+      <x:c r="K3" s="22" t="str"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="21" t="str"/>
@@ -439,12 +433,11 @@
       <x:c r="D4" s="12" t="str"/>
       <x:c r="E4" s="12" t="str"/>
       <x:c r="F4" s="12" t="str"/>
-      <x:c r="G4" s="12" t="str"/>
+      <x:c r="G4" s="14" t="str"/>
       <x:c r="H4" s="14" t="str"/>
-      <x:c r="I4" s="14" t="str"/>
-      <x:c r="J4" s="16" t="str"/>
-      <x:c r="K4" s="12" t="str"/>
-      <x:c r="L4" s="22" t="str"/>
+      <x:c r="I4" s="16" t="str"/>
+      <x:c r="J4" s="12" t="str"/>
+      <x:c r="K4" s="22" t="str"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="21" t="str"/>
@@ -453,12 +446,11 @@
       <x:c r="D5" s="12" t="str"/>
       <x:c r="E5" s="12" t="str"/>
       <x:c r="F5" s="12" t="str"/>
-      <x:c r="G5" s="12" t="str"/>
+      <x:c r="G5" s="14" t="str"/>
       <x:c r="H5" s="14" t="str"/>
-      <x:c r="I5" s="14" t="str"/>
-      <x:c r="J5" s="16" t="str"/>
-      <x:c r="K5" s="12" t="str"/>
-      <x:c r="L5" s="22" t="str"/>
+      <x:c r="I5" s="16" t="str"/>
+      <x:c r="J5" s="12" t="str"/>
+      <x:c r="K5" s="22" t="str"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="21" t="str"/>
@@ -467,12 +459,11 @@
       <x:c r="D6" s="12" t="str"/>
       <x:c r="E6" s="12" t="str"/>
       <x:c r="F6" s="12" t="str"/>
-      <x:c r="G6" s="12" t="str"/>
+      <x:c r="G6" s="14" t="str"/>
       <x:c r="H6" s="14" t="str"/>
-      <x:c r="I6" s="14" t="str"/>
-      <x:c r="J6" s="16" t="str"/>
-      <x:c r="K6" s="12" t="str"/>
-      <x:c r="L6" s="22" t="str"/>
+      <x:c r="I6" s="16" t="str"/>
+      <x:c r="J6" s="12" t="str"/>
+      <x:c r="K6" s="22" t="str"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="21" t="str"/>
@@ -481,12 +472,11 @@
       <x:c r="D7" s="12" t="str"/>
       <x:c r="E7" s="12" t="str"/>
       <x:c r="F7" s="12" t="str"/>
-      <x:c r="G7" s="12" t="str"/>
+      <x:c r="G7" s="14" t="str"/>
       <x:c r="H7" s="14" t="str"/>
-      <x:c r="I7" s="14" t="str"/>
-      <x:c r="J7" s="16" t="str"/>
-      <x:c r="K7" s="12" t="str"/>
-      <x:c r="L7" s="22" t="str"/>
+      <x:c r="I7" s="16" t="str"/>
+      <x:c r="J7" s="12" t="str"/>
+      <x:c r="K7" s="22" t="str"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="21" t="str"/>
@@ -495,12 +485,11 @@
       <x:c r="D8" s="12" t="str"/>
       <x:c r="E8" s="12" t="str"/>
       <x:c r="F8" s="12" t="str"/>
-      <x:c r="G8" s="12" t="str"/>
+      <x:c r="G8" s="14" t="str"/>
       <x:c r="H8" s="14" t="str"/>
-      <x:c r="I8" s="14" t="str"/>
-      <x:c r="J8" s="16" t="str"/>
-      <x:c r="K8" s="12" t="str"/>
-      <x:c r="L8" s="22" t="str"/>
+      <x:c r="I8" s="16" t="str"/>
+      <x:c r="J8" s="12" t="str"/>
+      <x:c r="K8" s="22" t="str"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="21" t="str"/>
@@ -509,12 +498,11 @@
       <x:c r="D9" s="12" t="str"/>
       <x:c r="E9" s="12" t="str"/>
       <x:c r="F9" s="12" t="str"/>
-      <x:c r="G9" s="12" t="str"/>
+      <x:c r="G9" s="14" t="str"/>
       <x:c r="H9" s="14" t="str"/>
-      <x:c r="I9" s="14" t="str"/>
-      <x:c r="J9" s="16" t="str"/>
-      <x:c r="K9" s="12" t="str"/>
-      <x:c r="L9" s="22" t="str"/>
+      <x:c r="I9" s="16" t="str"/>
+      <x:c r="J9" s="12" t="str"/>
+      <x:c r="K9" s="22" t="str"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="21" t="str"/>
@@ -523,12 +511,11 @@
       <x:c r="D10" s="12" t="str"/>
       <x:c r="E10" s="12" t="str"/>
       <x:c r="F10" s="12" t="str"/>
-      <x:c r="G10" s="12" t="str"/>
+      <x:c r="G10" s="14" t="str"/>
       <x:c r="H10" s="14" t="str"/>
-      <x:c r="I10" s="14" t="str"/>
-      <x:c r="J10" s="16" t="str"/>
-      <x:c r="K10" s="12" t="str"/>
-      <x:c r="L10" s="22" t="str"/>
+      <x:c r="I10" s="16" t="str"/>
+      <x:c r="J10" s="12" t="str"/>
+      <x:c r="K10" s="22" t="str"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="21" t="str"/>
@@ -537,12 +524,11 @@
       <x:c r="D11" s="12" t="str"/>
       <x:c r="E11" s="12" t="str"/>
       <x:c r="F11" s="12" t="str"/>
-      <x:c r="G11" s="12" t="str"/>
+      <x:c r="G11" s="14" t="str"/>
       <x:c r="H11" s="14" t="str"/>
-      <x:c r="I11" s="14" t="str"/>
-      <x:c r="J11" s="16" t="str"/>
-      <x:c r="K11" s="12" t="str"/>
-      <x:c r="L11" s="22" t="str"/>
+      <x:c r="I11" s="16" t="str"/>
+      <x:c r="J11" s="12" t="str"/>
+      <x:c r="K11" s="22" t="str"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="21" t="str"/>
@@ -551,12 +537,11 @@
       <x:c r="D12" s="12" t="str"/>
       <x:c r="E12" s="12" t="str"/>
       <x:c r="F12" s="12" t="str"/>
-      <x:c r="G12" s="12" t="str"/>
+      <x:c r="G12" s="14" t="str"/>
       <x:c r="H12" s="14" t="str"/>
-      <x:c r="I12" s="14" t="str"/>
-      <x:c r="J12" s="16" t="str"/>
-      <x:c r="K12" s="12" t="str"/>
-      <x:c r="L12" s="22" t="str"/>
+      <x:c r="I12" s="16" t="str"/>
+      <x:c r="J12" s="12" t="str"/>
+      <x:c r="K12" s="22" t="str"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="21" t="str"/>
@@ -565,12 +550,11 @@
       <x:c r="D13" s="12" t="str"/>
       <x:c r="E13" s="12" t="str"/>
       <x:c r="F13" s="12" t="str"/>
-      <x:c r="G13" s="12" t="str"/>
+      <x:c r="G13" s="14" t="str"/>
       <x:c r="H13" s="14" t="str"/>
-      <x:c r="I13" s="14" t="str"/>
-      <x:c r="J13" s="16" t="str"/>
-      <x:c r="K13" s="12" t="str"/>
-      <x:c r="L13" s="22" t="str"/>
+      <x:c r="I13" s="16" t="str"/>
+      <x:c r="J13" s="12" t="str"/>
+      <x:c r="K13" s="22" t="str"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="21" t="str"/>
@@ -579,12 +563,11 @@
       <x:c r="D14" s="12" t="str"/>
       <x:c r="E14" s="12" t="str"/>
       <x:c r="F14" s="12" t="str"/>
-      <x:c r="G14" s="12" t="str"/>
+      <x:c r="G14" s="14" t="str"/>
       <x:c r="H14" s="14" t="str"/>
-      <x:c r="I14" s="14" t="str"/>
-      <x:c r="J14" s="16" t="str"/>
-      <x:c r="K14" s="12" t="str"/>
-      <x:c r="L14" s="22" t="str"/>
+      <x:c r="I14" s="16" t="str"/>
+      <x:c r="J14" s="12" t="str"/>
+      <x:c r="K14" s="22" t="str"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="21" t="str"/>
@@ -593,12 +576,11 @@
       <x:c r="D15" s="12" t="str"/>
       <x:c r="E15" s="12" t="str"/>
       <x:c r="F15" s="12" t="str"/>
-      <x:c r="G15" s="12" t="str"/>
+      <x:c r="G15" s="14" t="str"/>
       <x:c r="H15" s="14" t="str"/>
-      <x:c r="I15" s="14" t="str"/>
-      <x:c r="J15" s="16" t="str"/>
-      <x:c r="K15" s="12" t="str"/>
-      <x:c r="L15" s="22" t="str"/>
+      <x:c r="I15" s="16" t="str"/>
+      <x:c r="J15" s="12" t="str"/>
+      <x:c r="K15" s="22" t="str"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="21" t="str"/>
@@ -607,12 +589,11 @@
       <x:c r="D16" s="12" t="str"/>
       <x:c r="E16" s="12" t="str"/>
       <x:c r="F16" s="12" t="str"/>
-      <x:c r="G16" s="12" t="str"/>
+      <x:c r="G16" s="14" t="str"/>
       <x:c r="H16" s="14" t="str"/>
-      <x:c r="I16" s="14" t="str"/>
-      <x:c r="J16" s="16" t="str"/>
-      <x:c r="K16" s="12" t="str"/>
-      <x:c r="L16" s="22" t="str"/>
+      <x:c r="I16" s="16" t="str"/>
+      <x:c r="J16" s="12" t="str"/>
+      <x:c r="K16" s="22" t="str"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="21" t="str"/>
@@ -621,12 +602,11 @@
       <x:c r="D17" s="12" t="str"/>
       <x:c r="E17" s="12" t="str"/>
       <x:c r="F17" s="12" t="str"/>
-      <x:c r="G17" s="12" t="str"/>
+      <x:c r="G17" s="14" t="str"/>
       <x:c r="H17" s="14" t="str"/>
-      <x:c r="I17" s="14" t="str"/>
-      <x:c r="J17" s="16" t="str"/>
-      <x:c r="K17" s="12" t="str"/>
-      <x:c r="L17" s="22" t="str"/>
+      <x:c r="I17" s="16" t="str"/>
+      <x:c r="J17" s="12" t="str"/>
+      <x:c r="K17" s="22" t="str"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="21" t="str"/>
@@ -635,12 +615,11 @@
       <x:c r="D18" s="12" t="str"/>
       <x:c r="E18" s="12" t="str"/>
       <x:c r="F18" s="12" t="str"/>
-      <x:c r="G18" s="12" t="str"/>
+      <x:c r="G18" s="14" t="str"/>
       <x:c r="H18" s="14" t="str"/>
-      <x:c r="I18" s="14" t="str"/>
-      <x:c r="J18" s="16" t="str"/>
-      <x:c r="K18" s="12" t="str"/>
-      <x:c r="L18" s="22" t="str"/>
+      <x:c r="I18" s="16" t="str"/>
+      <x:c r="J18" s="12" t="str"/>
+      <x:c r="K18" s="22" t="str"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="21" t="str"/>
@@ -649,12 +628,11 @@
       <x:c r="D19" s="12" t="str"/>
       <x:c r="E19" s="12" t="str"/>
       <x:c r="F19" s="12" t="str"/>
-      <x:c r="G19" s="12" t="str"/>
+      <x:c r="G19" s="14" t="str"/>
       <x:c r="H19" s="14" t="str"/>
-      <x:c r="I19" s="14" t="str"/>
-      <x:c r="J19" s="16" t="str"/>
-      <x:c r="K19" s="12" t="str"/>
-      <x:c r="L19" s="22" t="str"/>
+      <x:c r="I19" s="16" t="str"/>
+      <x:c r="J19" s="12" t="str"/>
+      <x:c r="K19" s="22" t="str"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="21" t="str"/>
@@ -663,12 +641,11 @@
       <x:c r="D20" s="12" t="str"/>
       <x:c r="E20" s="12" t="str"/>
       <x:c r="F20" s="12" t="str"/>
-      <x:c r="G20" s="12" t="str"/>
+      <x:c r="G20" s="14" t="str"/>
       <x:c r="H20" s="14" t="str"/>
-      <x:c r="I20" s="14" t="str"/>
-      <x:c r="J20" s="16" t="str"/>
-      <x:c r="K20" s="12" t="str"/>
-      <x:c r="L20" s="22" t="str"/>
+      <x:c r="I20" s="16" t="str"/>
+      <x:c r="J20" s="12" t="str"/>
+      <x:c r="K20" s="22" t="str"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="21" t="str"/>
@@ -677,12 +654,11 @@
       <x:c r="D21" s="12" t="str"/>
       <x:c r="E21" s="12" t="str"/>
       <x:c r="F21" s="12" t="str"/>
-      <x:c r="G21" s="12" t="str"/>
+      <x:c r="G21" s="14" t="str"/>
       <x:c r="H21" s="14" t="str"/>
-      <x:c r="I21" s="14" t="str"/>
-      <x:c r="J21" s="16" t="str"/>
-      <x:c r="K21" s="12" t="str"/>
-      <x:c r="L21" s="22" t="str"/>
+      <x:c r="I21" s="16" t="str"/>
+      <x:c r="J21" s="12" t="str"/>
+      <x:c r="K21" s="22" t="str"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="21" t="str"/>
@@ -691,12 +667,11 @@
       <x:c r="D22" s="12" t="str"/>
       <x:c r="E22" s="12" t="str"/>
       <x:c r="F22" s="12" t="str"/>
-      <x:c r="G22" s="12" t="str"/>
+      <x:c r="G22" s="14" t="str"/>
       <x:c r="H22" s="14" t="str"/>
-      <x:c r="I22" s="14" t="str"/>
-      <x:c r="J22" s="16" t="str"/>
-      <x:c r="K22" s="12" t="str"/>
-      <x:c r="L22" s="22" t="str"/>
+      <x:c r="I22" s="16" t="str"/>
+      <x:c r="J22" s="12" t="str"/>
+      <x:c r="K22" s="22" t="str"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="21" t="str"/>
@@ -705,12 +680,11 @@
       <x:c r="D23" s="12" t="str"/>
       <x:c r="E23" s="12" t="str"/>
       <x:c r="F23" s="12" t="str"/>
-      <x:c r="G23" s="12" t="str"/>
+      <x:c r="G23" s="14" t="str"/>
       <x:c r="H23" s="14" t="str"/>
-      <x:c r="I23" s="14" t="str"/>
-      <x:c r="J23" s="16" t="str"/>
-      <x:c r="K23" s="12" t="str"/>
-      <x:c r="L23" s="22" t="str"/>
+      <x:c r="I23" s="16" t="str"/>
+      <x:c r="J23" s="12" t="str"/>
+      <x:c r="K23" s="22" t="str"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="21" t="str"/>
@@ -719,12 +693,11 @@
       <x:c r="D24" s="12" t="str"/>
       <x:c r="E24" s="12" t="str"/>
       <x:c r="F24" s="12" t="str"/>
-      <x:c r="G24" s="12" t="str"/>
+      <x:c r="G24" s="14" t="str"/>
       <x:c r="H24" s="14" t="str"/>
-      <x:c r="I24" s="14" t="str"/>
-      <x:c r="J24" s="16" t="str"/>
-      <x:c r="K24" s="12" t="str"/>
-      <x:c r="L24" s="22" t="str"/>
+      <x:c r="I24" s="16" t="str"/>
+      <x:c r="J24" s="12" t="str"/>
+      <x:c r="K24" s="22" t="str"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="21" t="str"/>
@@ -733,12 +706,11 @@
       <x:c r="D25" s="12" t="str"/>
       <x:c r="E25" s="12" t="str"/>
       <x:c r="F25" s="12" t="str"/>
-      <x:c r="G25" s="12" t="str"/>
+      <x:c r="G25" s="14" t="str"/>
       <x:c r="H25" s="14" t="str"/>
-      <x:c r="I25" s="14" t="str"/>
-      <x:c r="J25" s="16" t="str"/>
-      <x:c r="K25" s="12" t="str"/>
-      <x:c r="L25" s="22" t="str"/>
+      <x:c r="I25" s="16" t="str"/>
+      <x:c r="J25" s="12" t="str"/>
+      <x:c r="K25" s="22" t="str"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="21" t="str"/>
@@ -747,12 +719,11 @@
       <x:c r="D26" s="12" t="str"/>
       <x:c r="E26" s="12" t="str"/>
       <x:c r="F26" s="12" t="str"/>
-      <x:c r="G26" s="12" t="str"/>
+      <x:c r="G26" s="14" t="str"/>
       <x:c r="H26" s="14" t="str"/>
-      <x:c r="I26" s="14" t="str"/>
-      <x:c r="J26" s="16" t="str"/>
-      <x:c r="K26" s="12" t="str"/>
-      <x:c r="L26" s="22" t="str"/>
+      <x:c r="I26" s="16" t="str"/>
+      <x:c r="J26" s="12" t="str"/>
+      <x:c r="K26" s="22" t="str"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="21" t="str"/>
@@ -761,12 +732,11 @@
       <x:c r="D27" s="12" t="str"/>
       <x:c r="E27" s="12" t="str"/>
       <x:c r="F27" s="12" t="str"/>
-      <x:c r="G27" s="12" t="str"/>
+      <x:c r="G27" s="14" t="str"/>
       <x:c r="H27" s="14" t="str"/>
-      <x:c r="I27" s="14" t="str"/>
-      <x:c r="J27" s="16" t="str"/>
-      <x:c r="K27" s="12" t="str"/>
-      <x:c r="L27" s="22" t="str"/>
+      <x:c r="I27" s="16" t="str"/>
+      <x:c r="J27" s="12" t="str"/>
+      <x:c r="K27" s="22" t="str"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="21" t="str"/>
@@ -775,12 +745,11 @@
       <x:c r="D28" s="12" t="str"/>
       <x:c r="E28" s="12" t="str"/>
       <x:c r="F28" s="12" t="str"/>
-      <x:c r="G28" s="12" t="str"/>
+      <x:c r="G28" s="14" t="str"/>
       <x:c r="H28" s="14" t="str"/>
-      <x:c r="I28" s="14" t="str"/>
-      <x:c r="J28" s="16" t="str"/>
-      <x:c r="K28" s="12" t="str"/>
-      <x:c r="L28" s="22" t="str"/>
+      <x:c r="I28" s="16" t="str"/>
+      <x:c r="J28" s="12" t="str"/>
+      <x:c r="K28" s="22" t="str"/>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="21" t="str"/>
@@ -789,12 +758,11 @@
       <x:c r="D29" s="12" t="str"/>
       <x:c r="E29" s="12" t="str"/>
       <x:c r="F29" s="12" t="str"/>
-      <x:c r="G29" s="12" t="str"/>
+      <x:c r="G29" s="14" t="str"/>
       <x:c r="H29" s="14" t="str"/>
-      <x:c r="I29" s="14" t="str"/>
-      <x:c r="J29" s="16" t="str"/>
-      <x:c r="K29" s="12" t="str"/>
-      <x:c r="L29" s="22" t="str"/>
+      <x:c r="I29" s="16" t="str"/>
+      <x:c r="J29" s="12" t="str"/>
+      <x:c r="K29" s="22" t="str"/>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="21" t="str"/>
@@ -803,12 +771,11 @@
       <x:c r="D30" s="12" t="str"/>
       <x:c r="E30" s="12" t="str"/>
       <x:c r="F30" s="12" t="str"/>
-      <x:c r="G30" s="12" t="str"/>
+      <x:c r="G30" s="14" t="str"/>
       <x:c r="H30" s="14" t="str"/>
-      <x:c r="I30" s="14" t="str"/>
-      <x:c r="J30" s="16" t="str"/>
-      <x:c r="K30" s="12" t="str"/>
-      <x:c r="L30" s="22" t="str"/>
+      <x:c r="I30" s="16" t="str"/>
+      <x:c r="J30" s="12" t="str"/>
+      <x:c r="K30" s="22" t="str"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="21" t="str"/>
@@ -817,12 +784,11 @@
       <x:c r="D31" s="12" t="str"/>
       <x:c r="E31" s="12" t="str"/>
       <x:c r="F31" s="12" t="str"/>
-      <x:c r="G31" s="12" t="str"/>
+      <x:c r="G31" s="14" t="str"/>
       <x:c r="H31" s="14" t="str"/>
-      <x:c r="I31" s="14" t="str"/>
-      <x:c r="J31" s="16" t="str"/>
-      <x:c r="K31" s="12" t="str"/>
-      <x:c r="L31" s="22" t="str"/>
+      <x:c r="I31" s="16" t="str"/>
+      <x:c r="J31" s="12" t="str"/>
+      <x:c r="K31" s="22" t="str"/>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="21" t="str"/>
@@ -831,12 +797,11 @@
       <x:c r="D32" s="12" t="str"/>
       <x:c r="E32" s="12" t="str"/>
       <x:c r="F32" s="12" t="str"/>
-      <x:c r="G32" s="12" t="str"/>
+      <x:c r="G32" s="14" t="str"/>
       <x:c r="H32" s="14" t="str"/>
-      <x:c r="I32" s="14" t="str"/>
-      <x:c r="J32" s="16" t="str"/>
-      <x:c r="K32" s="12" t="str"/>
-      <x:c r="L32" s="22" t="str"/>
+      <x:c r="I32" s="16" t="str"/>
+      <x:c r="J32" s="12" t="str"/>
+      <x:c r="K32" s="22" t="str"/>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="21" t="str"/>
@@ -845,12 +810,11 @@
       <x:c r="D33" s="12" t="str"/>
       <x:c r="E33" s="12" t="str"/>
       <x:c r="F33" s="12" t="str"/>
-      <x:c r="G33" s="12" t="str"/>
+      <x:c r="G33" s="14" t="str"/>
       <x:c r="H33" s="14" t="str"/>
-      <x:c r="I33" s="14" t="str"/>
-      <x:c r="J33" s="16" t="str"/>
-      <x:c r="K33" s="12" t="str"/>
-      <x:c r="L33" s="22" t="str"/>
+      <x:c r="I33" s="16" t="str"/>
+      <x:c r="J33" s="12" t="str"/>
+      <x:c r="K33" s="22" t="str"/>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="21" t="str"/>
@@ -859,12 +823,11 @@
       <x:c r="D34" s="12" t="str"/>
       <x:c r="E34" s="12" t="str"/>
       <x:c r="F34" s="12" t="str"/>
-      <x:c r="G34" s="12" t="str"/>
+      <x:c r="G34" s="14" t="str"/>
       <x:c r="H34" s="14" t="str"/>
-      <x:c r="I34" s="14" t="str"/>
-      <x:c r="J34" s="16" t="str"/>
-      <x:c r="K34" s="12" t="str"/>
-      <x:c r="L34" s="22" t="str"/>
+      <x:c r="I34" s="16" t="str"/>
+      <x:c r="J34" s="12" t="str"/>
+      <x:c r="K34" s="22" t="str"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="21" t="str"/>
@@ -873,12 +836,11 @@
       <x:c r="D35" s="12" t="str"/>
       <x:c r="E35" s="12" t="str"/>
       <x:c r="F35" s="12" t="str"/>
-      <x:c r="G35" s="12" t="str"/>
+      <x:c r="G35" s="14" t="str"/>
       <x:c r="H35" s="14" t="str"/>
-      <x:c r="I35" s="14" t="str"/>
-      <x:c r="J35" s="16" t="str"/>
-      <x:c r="K35" s="12" t="str"/>
-      <x:c r="L35" s="22" t="str"/>
+      <x:c r="I35" s="16" t="str"/>
+      <x:c r="J35" s="12" t="str"/>
+      <x:c r="K35" s="22" t="str"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="21" t="str"/>
@@ -887,12 +849,11 @@
       <x:c r="D36" s="12" t="str"/>
       <x:c r="E36" s="12" t="str"/>
       <x:c r="F36" s="12" t="str"/>
-      <x:c r="G36" s="12" t="str"/>
+      <x:c r="G36" s="14" t="str"/>
       <x:c r="H36" s="14" t="str"/>
-      <x:c r="I36" s="14" t="str"/>
-      <x:c r="J36" s="16" t="str"/>
-      <x:c r="K36" s="12" t="str"/>
-      <x:c r="L36" s="22" t="str"/>
+      <x:c r="I36" s="16" t="str"/>
+      <x:c r="J36" s="12" t="str"/>
+      <x:c r="K36" s="22" t="str"/>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="21" t="str"/>
@@ -901,12 +862,11 @@
       <x:c r="D37" s="12" t="str"/>
       <x:c r="E37" s="12" t="str"/>
       <x:c r="F37" s="12" t="str"/>
-      <x:c r="G37" s="12" t="str"/>
+      <x:c r="G37" s="14" t="str"/>
       <x:c r="H37" s="14" t="str"/>
-      <x:c r="I37" s="14" t="str"/>
-      <x:c r="J37" s="16" t="str"/>
-      <x:c r="K37" s="12" t="str"/>
-      <x:c r="L37" s="22" t="str"/>
+      <x:c r="I37" s="16" t="str"/>
+      <x:c r="J37" s="12" t="str"/>
+      <x:c r="K37" s="22" t="str"/>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="21" t="str"/>
@@ -915,12 +875,11 @@
       <x:c r="D38" s="12" t="str"/>
       <x:c r="E38" s="12" t="str"/>
       <x:c r="F38" s="12" t="str"/>
-      <x:c r="G38" s="12" t="str"/>
+      <x:c r="G38" s="14" t="str"/>
       <x:c r="H38" s="14" t="str"/>
-      <x:c r="I38" s="14" t="str"/>
-      <x:c r="J38" s="16" t="str"/>
-      <x:c r="K38" s="12" t="str"/>
-      <x:c r="L38" s="22" t="str"/>
+      <x:c r="I38" s="16" t="str"/>
+      <x:c r="J38" s="12" t="str"/>
+      <x:c r="K38" s="22" t="str"/>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="21" t="str"/>
@@ -929,12 +888,11 @@
       <x:c r="D39" s="12" t="str"/>
       <x:c r="E39" s="12" t="str"/>
       <x:c r="F39" s="12" t="str"/>
-      <x:c r="G39" s="12" t="str"/>
+      <x:c r="G39" s="14" t="str"/>
       <x:c r="H39" s="14" t="str"/>
-      <x:c r="I39" s="14" t="str"/>
-      <x:c r="J39" s="16" t="str"/>
-      <x:c r="K39" s="12" t="str"/>
-      <x:c r="L39" s="22" t="str"/>
+      <x:c r="I39" s="16" t="str"/>
+      <x:c r="J39" s="12" t="str"/>
+      <x:c r="K39" s="22" t="str"/>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="21" t="str"/>
@@ -943,12 +901,11 @@
       <x:c r="D40" s="12" t="str"/>
       <x:c r="E40" s="12" t="str"/>
       <x:c r="F40" s="12" t="str"/>
-      <x:c r="G40" s="12" t="str"/>
+      <x:c r="G40" s="14" t="str"/>
       <x:c r="H40" s="14" t="str"/>
-      <x:c r="I40" s="14" t="str"/>
-      <x:c r="J40" s="16" t="str"/>
-      <x:c r="K40" s="12" t="str"/>
-      <x:c r="L40" s="22" t="str"/>
+      <x:c r="I40" s="16" t="str"/>
+      <x:c r="J40" s="12" t="str"/>
+      <x:c r="K40" s="22" t="str"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="21" t="str"/>
@@ -957,12 +914,11 @@
       <x:c r="D41" s="12" t="str"/>
       <x:c r="E41" s="12" t="str"/>
       <x:c r="F41" s="12" t="str"/>
-      <x:c r="G41" s="12" t="str"/>
+      <x:c r="G41" s="14" t="str"/>
       <x:c r="H41" s="14" t="str"/>
-      <x:c r="I41" s="14" t="str"/>
-      <x:c r="J41" s="16" t="str"/>
-      <x:c r="K41" s="12" t="str"/>
-      <x:c r="L41" s="22" t="str"/>
+      <x:c r="I41" s="16" t="str"/>
+      <x:c r="J41" s="12" t="str"/>
+      <x:c r="K41" s="22" t="str"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="21" t="str"/>
@@ -971,12 +927,11 @@
       <x:c r="D42" s="12" t="str"/>
       <x:c r="E42" s="12" t="str"/>
       <x:c r="F42" s="12" t="str"/>
-      <x:c r="G42" s="12" t="str"/>
+      <x:c r="G42" s="14" t="str"/>
       <x:c r="H42" s="14" t="str"/>
-      <x:c r="I42" s="14" t="str"/>
-      <x:c r="J42" s="16" t="str"/>
-      <x:c r="K42" s="12" t="str"/>
-      <x:c r="L42" s="22" t="str"/>
+      <x:c r="I42" s="16" t="str"/>
+      <x:c r="J42" s="12" t="str"/>
+      <x:c r="K42" s="22" t="str"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="21" t="str"/>
@@ -985,12 +940,11 @@
       <x:c r="D43" s="12" t="str"/>
       <x:c r="E43" s="12" t="str"/>
       <x:c r="F43" s="12" t="str"/>
-      <x:c r="G43" s="12" t="str"/>
+      <x:c r="G43" s="14" t="str"/>
       <x:c r="H43" s="14" t="str"/>
-      <x:c r="I43" s="14" t="str"/>
-      <x:c r="J43" s="16" t="str"/>
-      <x:c r="K43" s="12" t="str"/>
-      <x:c r="L43" s="22" t="str"/>
+      <x:c r="I43" s="16" t="str"/>
+      <x:c r="J43" s="12" t="str"/>
+      <x:c r="K43" s="22" t="str"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="21" t="str"/>
@@ -999,12 +953,11 @@
       <x:c r="D44" s="12" t="str"/>
       <x:c r="E44" s="12" t="str"/>
       <x:c r="F44" s="12" t="str"/>
-      <x:c r="G44" s="12" t="str"/>
+      <x:c r="G44" s="14" t="str"/>
       <x:c r="H44" s="14" t="str"/>
-      <x:c r="I44" s="14" t="str"/>
-      <x:c r="J44" s="16" t="str"/>
-      <x:c r="K44" s="12" t="str"/>
-      <x:c r="L44" s="22" t="str"/>
+      <x:c r="I44" s="16" t="str"/>
+      <x:c r="J44" s="12" t="str"/>
+      <x:c r="K44" s="22" t="str"/>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="21" t="str"/>
@@ -1013,12 +966,11 @@
       <x:c r="D45" s="12" t="str"/>
       <x:c r="E45" s="12" t="str"/>
       <x:c r="F45" s="12" t="str"/>
-      <x:c r="G45" s="12" t="str"/>
+      <x:c r="G45" s="14" t="str"/>
       <x:c r="H45" s="14" t="str"/>
-      <x:c r="I45" s="14" t="str"/>
-      <x:c r="J45" s="16" t="str"/>
-      <x:c r="K45" s="12" t="str"/>
-      <x:c r="L45" s="22" t="str"/>
+      <x:c r="I45" s="16" t="str"/>
+      <x:c r="J45" s="12" t="str"/>
+      <x:c r="K45" s="22" t="str"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="21" t="str"/>
@@ -1027,12 +979,11 @@
       <x:c r="D46" s="12" t="str"/>
       <x:c r="E46" s="12" t="str"/>
       <x:c r="F46" s="12" t="str"/>
-      <x:c r="G46" s="12" t="str"/>
+      <x:c r="G46" s="14" t="str"/>
       <x:c r="H46" s="14" t="str"/>
-      <x:c r="I46" s="14" t="str"/>
-      <x:c r="J46" s="16" t="str"/>
-      <x:c r="K46" s="12" t="str"/>
-      <x:c r="L46" s="22" t="str"/>
+      <x:c r="I46" s="16" t="str"/>
+      <x:c r="J46" s="12" t="str"/>
+      <x:c r="K46" s="22" t="str"/>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="21" t="str"/>
@@ -1041,12 +992,11 @@
       <x:c r="D47" s="12" t="str"/>
       <x:c r="E47" s="12" t="str"/>
       <x:c r="F47" s="12" t="str"/>
-      <x:c r="G47" s="12" t="str"/>
+      <x:c r="G47" s="14" t="str"/>
       <x:c r="H47" s="14" t="str"/>
-      <x:c r="I47" s="14" t="str"/>
-      <x:c r="J47" s="16" t="str"/>
-      <x:c r="K47" s="12" t="str"/>
-      <x:c r="L47" s="22" t="str"/>
+      <x:c r="I47" s="16" t="str"/>
+      <x:c r="J47" s="12" t="str"/>
+      <x:c r="K47" s="22" t="str"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="21" t="str"/>
@@ -1055,12 +1005,11 @@
       <x:c r="D48" s="12" t="str"/>
       <x:c r="E48" s="12" t="str"/>
       <x:c r="F48" s="12" t="str"/>
-      <x:c r="G48" s="12" t="str"/>
+      <x:c r="G48" s="14" t="str"/>
       <x:c r="H48" s="14" t="str"/>
-      <x:c r="I48" s="14" t="str"/>
-      <x:c r="J48" s="16" t="str"/>
-      <x:c r="K48" s="12" t="str"/>
-      <x:c r="L48" s="22" t="str"/>
+      <x:c r="I48" s="16" t="str"/>
+      <x:c r="J48" s="12" t="str"/>
+      <x:c r="K48" s="22" t="str"/>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="21" t="str"/>
@@ -1069,12 +1018,11 @@
       <x:c r="D49" s="12" t="str"/>
       <x:c r="E49" s="12" t="str"/>
       <x:c r="F49" s="12" t="str"/>
-      <x:c r="G49" s="12" t="str"/>
+      <x:c r="G49" s="14" t="str"/>
       <x:c r="H49" s="14" t="str"/>
-      <x:c r="I49" s="14" t="str"/>
-      <x:c r="J49" s="16" t="str"/>
-      <x:c r="K49" s="12" t="str"/>
-      <x:c r="L49" s="22" t="str"/>
+      <x:c r="I49" s="16" t="str"/>
+      <x:c r="J49" s="12" t="str"/>
+      <x:c r="K49" s="22" t="str"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="21" t="str"/>
@@ -1083,12 +1031,11 @@
       <x:c r="D50" s="12" t="str"/>
       <x:c r="E50" s="12" t="str"/>
       <x:c r="F50" s="12" t="str"/>
-      <x:c r="G50" s="12" t="str"/>
+      <x:c r="G50" s="14" t="str"/>
       <x:c r="H50" s="14" t="str"/>
-      <x:c r="I50" s="14" t="str"/>
-      <x:c r="J50" s="16" t="str"/>
-      <x:c r="K50" s="12" t="str"/>
-      <x:c r="L50" s="22" t="str"/>
+      <x:c r="I50" s="16" t="str"/>
+      <x:c r="J50" s="12" t="str"/>
+      <x:c r="K50" s="22" t="str"/>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="21" t="str"/>
@@ -1097,12 +1044,11 @@
       <x:c r="D51" s="12" t="str"/>
       <x:c r="E51" s="12" t="str"/>
       <x:c r="F51" s="12" t="str"/>
-      <x:c r="G51" s="12" t="str"/>
+      <x:c r="G51" s="14" t="str"/>
       <x:c r="H51" s="14" t="str"/>
-      <x:c r="I51" s="14" t="str"/>
-      <x:c r="J51" s="16" t="str"/>
-      <x:c r="K51" s="12" t="str"/>
-      <x:c r="L51" s="22" t="str"/>
+      <x:c r="I51" s="16" t="str"/>
+      <x:c r="J51" s="12" t="str"/>
+      <x:c r="K51" s="22" t="str"/>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="21" t="str"/>
@@ -1111,12 +1057,11 @@
       <x:c r="D52" s="12" t="str"/>
       <x:c r="E52" s="12" t="str"/>
       <x:c r="F52" s="12" t="str"/>
-      <x:c r="G52" s="12" t="str"/>
+      <x:c r="G52" s="14" t="str"/>
       <x:c r="H52" s="14" t="str"/>
-      <x:c r="I52" s="14" t="str"/>
-      <x:c r="J52" s="16" t="str"/>
-      <x:c r="K52" s="12" t="str"/>
-      <x:c r="L52" s="22" t="str"/>
+      <x:c r="I52" s="16" t="str"/>
+      <x:c r="J52" s="12" t="str"/>
+      <x:c r="K52" s="22" t="str"/>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="21" t="str"/>
@@ -1125,12 +1070,11 @@
       <x:c r="D53" s="12" t="str"/>
       <x:c r="E53" s="12" t="str"/>
       <x:c r="F53" s="12" t="str"/>
-      <x:c r="G53" s="12" t="str"/>
+      <x:c r="G53" s="14" t="str"/>
       <x:c r="H53" s="14" t="str"/>
-      <x:c r="I53" s="14" t="str"/>
-      <x:c r="J53" s="16" t="str"/>
-      <x:c r="K53" s="12" t="str"/>
-      <x:c r="L53" s="22" t="str"/>
+      <x:c r="I53" s="16" t="str"/>
+      <x:c r="J53" s="12" t="str"/>
+      <x:c r="K53" s="22" t="str"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="21" t="str"/>
@@ -1139,12 +1083,11 @@
       <x:c r="D54" s="12" t="str"/>
       <x:c r="E54" s="12" t="str"/>
       <x:c r="F54" s="12" t="str"/>
-      <x:c r="G54" s="12" t="str"/>
+      <x:c r="G54" s="14" t="str"/>
       <x:c r="H54" s="14" t="str"/>
-      <x:c r="I54" s="14" t="str"/>
-      <x:c r="J54" s="16" t="str"/>
-      <x:c r="K54" s="12" t="str"/>
-      <x:c r="L54" s="22" t="str"/>
+      <x:c r="I54" s="16" t="str"/>
+      <x:c r="J54" s="12" t="str"/>
+      <x:c r="K54" s="22" t="str"/>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="21" t="str"/>
@@ -1153,12 +1096,11 @@
       <x:c r="D55" s="12" t="str"/>
       <x:c r="E55" s="12" t="str"/>
       <x:c r="F55" s="12" t="str"/>
-      <x:c r="G55" s="12" t="str"/>
+      <x:c r="G55" s="14" t="str"/>
       <x:c r="H55" s="14" t="str"/>
-      <x:c r="I55" s="14" t="str"/>
-      <x:c r="J55" s="16" t="str"/>
-      <x:c r="K55" s="12" t="str"/>
-      <x:c r="L55" s="22" t="str"/>
+      <x:c r="I55" s="16" t="str"/>
+      <x:c r="J55" s="12" t="str"/>
+      <x:c r="K55" s="22" t="str"/>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="21" t="str"/>
@@ -1167,12 +1109,11 @@
       <x:c r="D56" s="12" t="str"/>
       <x:c r="E56" s="12" t="str"/>
       <x:c r="F56" s="12" t="str"/>
-      <x:c r="G56" s="12" t="str"/>
+      <x:c r="G56" s="14" t="str"/>
       <x:c r="H56" s="14" t="str"/>
-      <x:c r="I56" s="14" t="str"/>
-      <x:c r="J56" s="16" t="str"/>
-      <x:c r="K56" s="12" t="str"/>
-      <x:c r="L56" s="22" t="str"/>
+      <x:c r="I56" s="16" t="str"/>
+      <x:c r="J56" s="12" t="str"/>
+      <x:c r="K56" s="22" t="str"/>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="21" t="str"/>
@@ -1181,12 +1122,11 @@
       <x:c r="D57" s="12" t="str"/>
       <x:c r="E57" s="12" t="str"/>
       <x:c r="F57" s="12" t="str"/>
-      <x:c r="G57" s="12" t="str"/>
+      <x:c r="G57" s="14" t="str"/>
       <x:c r="H57" s="14" t="str"/>
-      <x:c r="I57" s="14" t="str"/>
-      <x:c r="J57" s="16" t="str"/>
-      <x:c r="K57" s="12" t="str"/>
-      <x:c r="L57" s="22" t="str"/>
+      <x:c r="I57" s="16" t="str"/>
+      <x:c r="J57" s="12" t="str"/>
+      <x:c r="K57" s="22" t="str"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="21" t="str"/>
@@ -1195,12 +1135,11 @@
       <x:c r="D58" s="12" t="str"/>
       <x:c r="E58" s="12" t="str"/>
       <x:c r="F58" s="12" t="str"/>
-      <x:c r="G58" s="12" t="str"/>
+      <x:c r="G58" s="14" t="str"/>
       <x:c r="H58" s="14" t="str"/>
-      <x:c r="I58" s="14" t="str"/>
-      <x:c r="J58" s="16" t="str"/>
-      <x:c r="K58" s="12" t="str"/>
-      <x:c r="L58" s="22" t="str"/>
+      <x:c r="I58" s="16" t="str"/>
+      <x:c r="J58" s="12" t="str"/>
+      <x:c r="K58" s="22" t="str"/>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="21" t="str"/>
@@ -1209,12 +1148,11 @@
       <x:c r="D59" s="12" t="str"/>
       <x:c r="E59" s="12" t="str"/>
       <x:c r="F59" s="12" t="str"/>
-      <x:c r="G59" s="12" t="str"/>
+      <x:c r="G59" s="14" t="str"/>
       <x:c r="H59" s="14" t="str"/>
-      <x:c r="I59" s="14" t="str"/>
-      <x:c r="J59" s="16" t="str"/>
-      <x:c r="K59" s="12" t="str"/>
-      <x:c r="L59" s="22" t="str"/>
+      <x:c r="I59" s="16" t="str"/>
+      <x:c r="J59" s="12" t="str"/>
+      <x:c r="K59" s="22" t="str"/>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="21" t="str"/>
@@ -1223,12 +1161,11 @@
       <x:c r="D60" s="12" t="str"/>
       <x:c r="E60" s="12" t="str"/>
       <x:c r="F60" s="12" t="str"/>
-      <x:c r="G60" s="12" t="str"/>
+      <x:c r="G60" s="14" t="str"/>
       <x:c r="H60" s="14" t="str"/>
-      <x:c r="I60" s="14" t="str"/>
-      <x:c r="J60" s="16" t="str"/>
-      <x:c r="K60" s="12" t="str"/>
-      <x:c r="L60" s="22" t="str"/>
+      <x:c r="I60" s="16" t="str"/>
+      <x:c r="J60" s="12" t="str"/>
+      <x:c r="K60" s="22" t="str"/>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="21" t="str"/>
@@ -1237,12 +1174,11 @@
       <x:c r="D61" s="12" t="str"/>
       <x:c r="E61" s="12" t="str"/>
       <x:c r="F61" s="12" t="str"/>
-      <x:c r="G61" s="12" t="str"/>
+      <x:c r="G61" s="14" t="str"/>
       <x:c r="H61" s="14" t="str"/>
-      <x:c r="I61" s="14" t="str"/>
-      <x:c r="J61" s="16" t="str"/>
-      <x:c r="K61" s="12" t="str"/>
-      <x:c r="L61" s="22" t="str"/>
+      <x:c r="I61" s="16" t="str"/>
+      <x:c r="J61" s="12" t="str"/>
+      <x:c r="K61" s="22" t="str"/>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="21" t="str"/>
@@ -1251,12 +1187,11 @@
       <x:c r="D62" s="12" t="str"/>
       <x:c r="E62" s="12" t="str"/>
       <x:c r="F62" s="12" t="str"/>
-      <x:c r="G62" s="12" t="str"/>
+      <x:c r="G62" s="14" t="str"/>
       <x:c r="H62" s="14" t="str"/>
-      <x:c r="I62" s="14" t="str"/>
-      <x:c r="J62" s="16" t="str"/>
-      <x:c r="K62" s="12" t="str"/>
-      <x:c r="L62" s="22" t="str"/>
+      <x:c r="I62" s="16" t="str"/>
+      <x:c r="J62" s="12" t="str"/>
+      <x:c r="K62" s="22" t="str"/>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="21" t="str"/>
@@ -1265,12 +1200,11 @@
       <x:c r="D63" s="12" t="str"/>
       <x:c r="E63" s="12" t="str"/>
       <x:c r="F63" s="12" t="str"/>
-      <x:c r="G63" s="12" t="str"/>
+      <x:c r="G63" s="14" t="str"/>
       <x:c r="H63" s="14" t="str"/>
-      <x:c r="I63" s="14" t="str"/>
-      <x:c r="J63" s="16" t="str"/>
-      <x:c r="K63" s="12" t="str"/>
-      <x:c r="L63" s="22" t="str"/>
+      <x:c r="I63" s="16" t="str"/>
+      <x:c r="J63" s="12" t="str"/>
+      <x:c r="K63" s="22" t="str"/>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="21" t="str"/>
@@ -1279,12 +1213,11 @@
       <x:c r="D64" s="12" t="str"/>
       <x:c r="E64" s="12" t="str"/>
       <x:c r="F64" s="12" t="str"/>
-      <x:c r="G64" s="12" t="str"/>
+      <x:c r="G64" s="14" t="str"/>
       <x:c r="H64" s="14" t="str"/>
-      <x:c r="I64" s="14" t="str"/>
-      <x:c r="J64" s="16" t="str"/>
-      <x:c r="K64" s="12" t="str"/>
-      <x:c r="L64" s="22" t="str"/>
+      <x:c r="I64" s="16" t="str"/>
+      <x:c r="J64" s="12" t="str"/>
+      <x:c r="K64" s="22" t="str"/>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="21" t="str"/>
@@ -1293,12 +1226,11 @@
       <x:c r="D65" s="12" t="str"/>
       <x:c r="E65" s="12" t="str"/>
       <x:c r="F65" s="12" t="str"/>
-      <x:c r="G65" s="12" t="str"/>
+      <x:c r="G65" s="14" t="str"/>
       <x:c r="H65" s="14" t="str"/>
-      <x:c r="I65" s="14" t="str"/>
-      <x:c r="J65" s="16" t="str"/>
-      <x:c r="K65" s="12" t="str"/>
-      <x:c r="L65" s="22" t="str"/>
+      <x:c r="I65" s="16" t="str"/>
+      <x:c r="J65" s="12" t="str"/>
+      <x:c r="K65" s="22" t="str"/>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="21" t="str"/>
@@ -1307,12 +1239,11 @@
       <x:c r="D66" s="12" t="str"/>
       <x:c r="E66" s="12" t="str"/>
       <x:c r="F66" s="12" t="str"/>
-      <x:c r="G66" s="12" t="str"/>
+      <x:c r="G66" s="14" t="str"/>
       <x:c r="H66" s="14" t="str"/>
-      <x:c r="I66" s="14" t="str"/>
-      <x:c r="J66" s="16" t="str"/>
-      <x:c r="K66" s="12" t="str"/>
-      <x:c r="L66" s="22" t="str"/>
+      <x:c r="I66" s="16" t="str"/>
+      <x:c r="J66" s="12" t="str"/>
+      <x:c r="K66" s="22" t="str"/>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="21" t="str"/>
@@ -1321,12 +1252,11 @@
       <x:c r="D67" s="12" t="str"/>
       <x:c r="E67" s="12" t="str"/>
       <x:c r="F67" s="12" t="str"/>
-      <x:c r="G67" s="12" t="str"/>
+      <x:c r="G67" s="14" t="str"/>
       <x:c r="H67" s="14" t="str"/>
-      <x:c r="I67" s="14" t="str"/>
-      <x:c r="J67" s="16" t="str"/>
-      <x:c r="K67" s="12" t="str"/>
-      <x:c r="L67" s="22" t="str"/>
+      <x:c r="I67" s="16" t="str"/>
+      <x:c r="J67" s="12" t="str"/>
+      <x:c r="K67" s="22" t="str"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="21" t="str"/>
@@ -1335,12 +1265,11 @@
       <x:c r="D68" s="12" t="str"/>
       <x:c r="E68" s="12" t="str"/>
       <x:c r="F68" s="12" t="str"/>
-      <x:c r="G68" s="12" t="str"/>
+      <x:c r="G68" s="14" t="str"/>
       <x:c r="H68" s="14" t="str"/>
-      <x:c r="I68" s="14" t="str"/>
-      <x:c r="J68" s="16" t="str"/>
-      <x:c r="K68" s="12" t="str"/>
-      <x:c r="L68" s="22" t="str"/>
+      <x:c r="I68" s="16" t="str"/>
+      <x:c r="J68" s="12" t="str"/>
+      <x:c r="K68" s="22" t="str"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="21" t="str"/>
@@ -1349,12 +1278,11 @@
       <x:c r="D69" s="12" t="str"/>
       <x:c r="E69" s="12" t="str"/>
       <x:c r="F69" s="12" t="str"/>
-      <x:c r="G69" s="12" t="str"/>
+      <x:c r="G69" s="14" t="str"/>
       <x:c r="H69" s="14" t="str"/>
-      <x:c r="I69" s="14" t="str"/>
-      <x:c r="J69" s="16" t="str"/>
-      <x:c r="K69" s="12" t="str"/>
-      <x:c r="L69" s="22" t="str"/>
+      <x:c r="I69" s="16" t="str"/>
+      <x:c r="J69" s="12" t="str"/>
+      <x:c r="K69" s="22" t="str"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="21" t="str"/>
@@ -1363,12 +1291,11 @@
       <x:c r="D70" s="12" t="str"/>
       <x:c r="E70" s="12" t="str"/>
       <x:c r="F70" s="12" t="str"/>
-      <x:c r="G70" s="12" t="str"/>
+      <x:c r="G70" s="14" t="str"/>
       <x:c r="H70" s="14" t="str"/>
-      <x:c r="I70" s="14" t="str"/>
-      <x:c r="J70" s="16" t="str"/>
-      <x:c r="K70" s="12" t="str"/>
-      <x:c r="L70" s="22" t="str"/>
+      <x:c r="I70" s="16" t="str"/>
+      <x:c r="J70" s="12" t="str"/>
+      <x:c r="K70" s="22" t="str"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="21" t="str"/>
@@ -1377,12 +1304,11 @@
       <x:c r="D71" s="12" t="str"/>
       <x:c r="E71" s="12" t="str"/>
       <x:c r="F71" s="12" t="str"/>
-      <x:c r="G71" s="12" t="str"/>
+      <x:c r="G71" s="14" t="str"/>
       <x:c r="H71" s="14" t="str"/>
-      <x:c r="I71" s="14" t="str"/>
-      <x:c r="J71" s="16" t="str"/>
-      <x:c r="K71" s="12" t="str"/>
-      <x:c r="L71" s="22" t="str"/>
+      <x:c r="I71" s="16" t="str"/>
+      <x:c r="J71" s="12" t="str"/>
+      <x:c r="K71" s="22" t="str"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="21" t="str"/>
@@ -1391,12 +1317,11 @@
       <x:c r="D72" s="12" t="str"/>
       <x:c r="E72" s="12" t="str"/>
       <x:c r="F72" s="12" t="str"/>
-      <x:c r="G72" s="12" t="str"/>
+      <x:c r="G72" s="14" t="str"/>
       <x:c r="H72" s="14" t="str"/>
-      <x:c r="I72" s="14" t="str"/>
-      <x:c r="J72" s="16" t="str"/>
-      <x:c r="K72" s="12" t="str"/>
-      <x:c r="L72" s="22" t="str"/>
+      <x:c r="I72" s="16" t="str"/>
+      <x:c r="J72" s="12" t="str"/>
+      <x:c r="K72" s="22" t="str"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="21" t="str"/>
@@ -1405,12 +1330,11 @@
       <x:c r="D73" s="12" t="str"/>
       <x:c r="E73" s="12" t="str"/>
       <x:c r="F73" s="12" t="str"/>
-      <x:c r="G73" s="12" t="str"/>
+      <x:c r="G73" s="14" t="str"/>
       <x:c r="H73" s="14" t="str"/>
-      <x:c r="I73" s="14" t="str"/>
-      <x:c r="J73" s="16" t="str"/>
-      <x:c r="K73" s="12" t="str"/>
-      <x:c r="L73" s="22" t="str"/>
+      <x:c r="I73" s="16" t="str"/>
+      <x:c r="J73" s="12" t="str"/>
+      <x:c r="K73" s="22" t="str"/>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="21" t="str"/>
@@ -1419,12 +1343,11 @@
       <x:c r="D74" s="12" t="str"/>
       <x:c r="E74" s="12" t="str"/>
       <x:c r="F74" s="12" t="str"/>
-      <x:c r="G74" s="12" t="str"/>
+      <x:c r="G74" s="14" t="str"/>
       <x:c r="H74" s="14" t="str"/>
-      <x:c r="I74" s="14" t="str"/>
-      <x:c r="J74" s="16" t="str"/>
-      <x:c r="K74" s="12" t="str"/>
-      <x:c r="L74" s="22" t="str"/>
+      <x:c r="I74" s="16" t="str"/>
+      <x:c r="J74" s="12" t="str"/>
+      <x:c r="K74" s="22" t="str"/>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="21" t="str"/>
@@ -1433,12 +1356,11 @@
       <x:c r="D75" s="12" t="str"/>
       <x:c r="E75" s="12" t="str"/>
       <x:c r="F75" s="12" t="str"/>
-      <x:c r="G75" s="12" t="str"/>
+      <x:c r="G75" s="14" t="str"/>
       <x:c r="H75" s="14" t="str"/>
-      <x:c r="I75" s="14" t="str"/>
-      <x:c r="J75" s="16" t="str"/>
-      <x:c r="K75" s="12" t="str"/>
-      <x:c r="L75" s="22" t="str"/>
+      <x:c r="I75" s="16" t="str"/>
+      <x:c r="J75" s="12" t="str"/>
+      <x:c r="K75" s="22" t="str"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="21" t="str"/>
@@ -1447,12 +1369,11 @@
       <x:c r="D76" s="12" t="str"/>
       <x:c r="E76" s="12" t="str"/>
       <x:c r="F76" s="12" t="str"/>
-      <x:c r="G76" s="12" t="str"/>
+      <x:c r="G76" s="14" t="str"/>
       <x:c r="H76" s="14" t="str"/>
-      <x:c r="I76" s="14" t="str"/>
-      <x:c r="J76" s="16" t="str"/>
-      <x:c r="K76" s="12" t="str"/>
-      <x:c r="L76" s="22" t="str"/>
+      <x:c r="I76" s="16" t="str"/>
+      <x:c r="J76" s="12" t="str"/>
+      <x:c r="K76" s="22" t="str"/>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="21" t="str"/>
@@ -1461,12 +1382,11 @@
       <x:c r="D77" s="12" t="str"/>
       <x:c r="E77" s="12" t="str"/>
       <x:c r="F77" s="12" t="str"/>
-      <x:c r="G77" s="12" t="str"/>
+      <x:c r="G77" s="14" t="str"/>
       <x:c r="H77" s="14" t="str"/>
-      <x:c r="I77" s="14" t="str"/>
-      <x:c r="J77" s="16" t="str"/>
-      <x:c r="K77" s="12" t="str"/>
-      <x:c r="L77" s="22" t="str"/>
+      <x:c r="I77" s="16" t="str"/>
+      <x:c r="J77" s="12" t="str"/>
+      <x:c r="K77" s="22" t="str"/>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="21" t="str"/>
@@ -1475,12 +1395,11 @@
       <x:c r="D78" s="12" t="str"/>
       <x:c r="E78" s="12" t="str"/>
       <x:c r="F78" s="12" t="str"/>
-      <x:c r="G78" s="12" t="str"/>
+      <x:c r="G78" s="14" t="str"/>
       <x:c r="H78" s="14" t="str"/>
-      <x:c r="I78" s="14" t="str"/>
-      <x:c r="J78" s="16" t="str"/>
-      <x:c r="K78" s="12" t="str"/>
-      <x:c r="L78" s="22" t="str"/>
+      <x:c r="I78" s="16" t="str"/>
+      <x:c r="J78" s="12" t="str"/>
+      <x:c r="K78" s="22" t="str"/>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="21" t="str"/>
@@ -1489,12 +1408,11 @@
       <x:c r="D79" s="12" t="str"/>
       <x:c r="E79" s="12" t="str"/>
       <x:c r="F79" s="12" t="str"/>
-      <x:c r="G79" s="12" t="str"/>
+      <x:c r="G79" s="14" t="str"/>
       <x:c r="H79" s="14" t="str"/>
-      <x:c r="I79" s="14" t="str"/>
-      <x:c r="J79" s="16" t="str"/>
-      <x:c r="K79" s="12" t="str"/>
-      <x:c r="L79" s="22" t="str"/>
+      <x:c r="I79" s="16" t="str"/>
+      <x:c r="J79" s="12" t="str"/>
+      <x:c r="K79" s="22" t="str"/>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="21" t="str"/>
@@ -1503,12 +1421,11 @@
       <x:c r="D80" s="12" t="str"/>
       <x:c r="E80" s="12" t="str"/>
       <x:c r="F80" s="12" t="str"/>
-      <x:c r="G80" s="12" t="str"/>
+      <x:c r="G80" s="14" t="str"/>
       <x:c r="H80" s="14" t="str"/>
-      <x:c r="I80" s="14" t="str"/>
-      <x:c r="J80" s="16" t="str"/>
-      <x:c r="K80" s="12" t="str"/>
-      <x:c r="L80" s="22" t="str"/>
+      <x:c r="I80" s="16" t="str"/>
+      <x:c r="J80" s="12" t="str"/>
+      <x:c r="K80" s="22" t="str"/>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="21" t="str"/>
@@ -1517,12 +1434,11 @@
       <x:c r="D81" s="12" t="str"/>
       <x:c r="E81" s="12" t="str"/>
       <x:c r="F81" s="12" t="str"/>
-      <x:c r="G81" s="12" t="str"/>
+      <x:c r="G81" s="14" t="str"/>
       <x:c r="H81" s="14" t="str"/>
-      <x:c r="I81" s="14" t="str"/>
-      <x:c r="J81" s="16" t="str"/>
-      <x:c r="K81" s="12" t="str"/>
-      <x:c r="L81" s="22" t="str"/>
+      <x:c r="I81" s="16" t="str"/>
+      <x:c r="J81" s="12" t="str"/>
+      <x:c r="K81" s="22" t="str"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="21" t="str"/>
@@ -1531,12 +1447,11 @@
       <x:c r="D82" s="12" t="str"/>
       <x:c r="E82" s="12" t="str"/>
       <x:c r="F82" s="12" t="str"/>
-      <x:c r="G82" s="12" t="str"/>
+      <x:c r="G82" s="14" t="str"/>
       <x:c r="H82" s="14" t="str"/>
-      <x:c r="I82" s="14" t="str"/>
-      <x:c r="J82" s="16" t="str"/>
-      <x:c r="K82" s="12" t="str"/>
-      <x:c r="L82" s="22" t="str"/>
+      <x:c r="I82" s="16" t="str"/>
+      <x:c r="J82" s="12" t="str"/>
+      <x:c r="K82" s="22" t="str"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="21" t="str"/>
@@ -1545,12 +1460,11 @@
       <x:c r="D83" s="12" t="str"/>
       <x:c r="E83" s="12" t="str"/>
       <x:c r="F83" s="12" t="str"/>
-      <x:c r="G83" s="12" t="str"/>
+      <x:c r="G83" s="14" t="str"/>
       <x:c r="H83" s="14" t="str"/>
-      <x:c r="I83" s="14" t="str"/>
-      <x:c r="J83" s="16" t="str"/>
-      <x:c r="K83" s="12" t="str"/>
-      <x:c r="L83" s="22" t="str"/>
+      <x:c r="I83" s="16" t="str"/>
+      <x:c r="J83" s="12" t="str"/>
+      <x:c r="K83" s="22" t="str"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="21" t="str"/>
@@ -1559,12 +1473,11 @@
       <x:c r="D84" s="12" t="str"/>
       <x:c r="E84" s="12" t="str"/>
       <x:c r="F84" s="12" t="str"/>
-      <x:c r="G84" s="12" t="str"/>
+      <x:c r="G84" s="14" t="str"/>
       <x:c r="H84" s="14" t="str"/>
-      <x:c r="I84" s="14" t="str"/>
-      <x:c r="J84" s="16" t="str"/>
-      <x:c r="K84" s="12" t="str"/>
-      <x:c r="L84" s="22" t="str"/>
+      <x:c r="I84" s="16" t="str"/>
+      <x:c r="J84" s="12" t="str"/>
+      <x:c r="K84" s="22" t="str"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="21" t="str"/>
@@ -1573,12 +1486,11 @@
       <x:c r="D85" s="12" t="str"/>
       <x:c r="E85" s="12" t="str"/>
       <x:c r="F85" s="12" t="str"/>
-      <x:c r="G85" s="12" t="str"/>
+      <x:c r="G85" s="14" t="str"/>
       <x:c r="H85" s="14" t="str"/>
-      <x:c r="I85" s="14" t="str"/>
-      <x:c r="J85" s="16" t="str"/>
-      <x:c r="K85" s="12" t="str"/>
-      <x:c r="L85" s="22" t="str"/>
+      <x:c r="I85" s="16" t="str"/>
+      <x:c r="J85" s="12" t="str"/>
+      <x:c r="K85" s="22" t="str"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="21" t="str"/>
@@ -1587,12 +1499,11 @@
       <x:c r="D86" s="12" t="str"/>
       <x:c r="E86" s="12" t="str"/>
       <x:c r="F86" s="12" t="str"/>
-      <x:c r="G86" s="12" t="str"/>
+      <x:c r="G86" s="14" t="str"/>
       <x:c r="H86" s="14" t="str"/>
-      <x:c r="I86" s="14" t="str"/>
-      <x:c r="J86" s="16" t="str"/>
-      <x:c r="K86" s="12" t="str"/>
-      <x:c r="L86" s="22" t="str"/>
+      <x:c r="I86" s="16" t="str"/>
+      <x:c r="J86" s="12" t="str"/>
+      <x:c r="K86" s="22" t="str"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="21" t="str"/>
@@ -1601,12 +1512,11 @@
       <x:c r="D87" s="12" t="str"/>
       <x:c r="E87" s="12" t="str"/>
       <x:c r="F87" s="12" t="str"/>
-      <x:c r="G87" s="12" t="str"/>
+      <x:c r="G87" s="14" t="str"/>
       <x:c r="H87" s="14" t="str"/>
-      <x:c r="I87" s="14" t="str"/>
-      <x:c r="J87" s="16" t="str"/>
-      <x:c r="K87" s="12" t="str"/>
-      <x:c r="L87" s="22" t="str"/>
+      <x:c r="I87" s="16" t="str"/>
+      <x:c r="J87" s="12" t="str"/>
+      <x:c r="K87" s="22" t="str"/>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="21" t="str"/>
@@ -1615,12 +1525,11 @@
       <x:c r="D88" s="12" t="str"/>
       <x:c r="E88" s="12" t="str"/>
       <x:c r="F88" s="12" t="str"/>
-      <x:c r="G88" s="12" t="str"/>
+      <x:c r="G88" s="14" t="str"/>
       <x:c r="H88" s="14" t="str"/>
-      <x:c r="I88" s="14" t="str"/>
-      <x:c r="J88" s="16" t="str"/>
-      <x:c r="K88" s="12" t="str"/>
-      <x:c r="L88" s="22" t="str"/>
+      <x:c r="I88" s="16" t="str"/>
+      <x:c r="J88" s="12" t="str"/>
+      <x:c r="K88" s="22" t="str"/>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="21" t="str"/>
@@ -1629,12 +1538,11 @@
       <x:c r="D89" s="12" t="str"/>
       <x:c r="E89" s="12" t="str"/>
       <x:c r="F89" s="12" t="str"/>
-      <x:c r="G89" s="12" t="str"/>
+      <x:c r="G89" s="14" t="str"/>
       <x:c r="H89" s="14" t="str"/>
-      <x:c r="I89" s="14" t="str"/>
-      <x:c r="J89" s="16" t="str"/>
-      <x:c r="K89" s="12" t="str"/>
-      <x:c r="L89" s="22" t="str"/>
+      <x:c r="I89" s="16" t="str"/>
+      <x:c r="J89" s="12" t="str"/>
+      <x:c r="K89" s="22" t="str"/>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="21" t="str"/>
@@ -1643,12 +1551,11 @@
       <x:c r="D90" s="12" t="str"/>
       <x:c r="E90" s="12" t="str"/>
       <x:c r="F90" s="12" t="str"/>
-      <x:c r="G90" s="12" t="str"/>
+      <x:c r="G90" s="14" t="str"/>
       <x:c r="H90" s="14" t="str"/>
-      <x:c r="I90" s="14" t="str"/>
-      <x:c r="J90" s="16" t="str"/>
-      <x:c r="K90" s="12" t="str"/>
-      <x:c r="L90" s="22" t="str"/>
+      <x:c r="I90" s="16" t="str"/>
+      <x:c r="J90" s="12" t="str"/>
+      <x:c r="K90" s="22" t="str"/>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="21" t="str"/>
@@ -1657,12 +1564,11 @@
       <x:c r="D91" s="12" t="str"/>
       <x:c r="E91" s="12" t="str"/>
       <x:c r="F91" s="12" t="str"/>
-      <x:c r="G91" s="12" t="str"/>
+      <x:c r="G91" s="14" t="str"/>
       <x:c r="H91" s="14" t="str"/>
-      <x:c r="I91" s="14" t="str"/>
-      <x:c r="J91" s="16" t="str"/>
-      <x:c r="K91" s="12" t="str"/>
-      <x:c r="L91" s="22" t="str"/>
+      <x:c r="I91" s="16" t="str"/>
+      <x:c r="J91" s="12" t="str"/>
+      <x:c r="K91" s="22" t="str"/>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="21" t="str"/>
@@ -1671,12 +1577,11 @@
       <x:c r="D92" s="12" t="str"/>
       <x:c r="E92" s="12" t="str"/>
       <x:c r="F92" s="12" t="str"/>
-      <x:c r="G92" s="12" t="str"/>
+      <x:c r="G92" s="14" t="str"/>
       <x:c r="H92" s="14" t="str"/>
-      <x:c r="I92" s="14" t="str"/>
-      <x:c r="J92" s="16" t="str"/>
-      <x:c r="K92" s="12" t="str"/>
-      <x:c r="L92" s="22" t="str"/>
+      <x:c r="I92" s="16" t="str"/>
+      <x:c r="J92" s="12" t="str"/>
+      <x:c r="K92" s="22" t="str"/>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="21" t="str"/>
@@ -1685,12 +1590,11 @@
       <x:c r="D93" s="12" t="str"/>
       <x:c r="E93" s="12" t="str"/>
       <x:c r="F93" s="12" t="str"/>
-      <x:c r="G93" s="12" t="str"/>
+      <x:c r="G93" s="14" t="str"/>
       <x:c r="H93" s="14" t="str"/>
-      <x:c r="I93" s="14" t="str"/>
-      <x:c r="J93" s="16" t="str"/>
-      <x:c r="K93" s="12" t="str"/>
-      <x:c r="L93" s="22" t="str"/>
+      <x:c r="I93" s="16" t="str"/>
+      <x:c r="J93" s="12" t="str"/>
+      <x:c r="K93" s="22" t="str"/>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="21" t="str"/>
@@ -1699,12 +1603,11 @@
       <x:c r="D94" s="12" t="str"/>
       <x:c r="E94" s="12" t="str"/>
       <x:c r="F94" s="12" t="str"/>
-      <x:c r="G94" s="12" t="str"/>
+      <x:c r="G94" s="14" t="str"/>
       <x:c r="H94" s="14" t="str"/>
-      <x:c r="I94" s="14" t="str"/>
-      <x:c r="J94" s="16" t="str"/>
-      <x:c r="K94" s="12" t="str"/>
-      <x:c r="L94" s="22" t="str"/>
+      <x:c r="I94" s="16" t="str"/>
+      <x:c r="J94" s="12" t="str"/>
+      <x:c r="K94" s="22" t="str"/>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="21" t="str"/>
@@ -1713,12 +1616,11 @@
       <x:c r="D95" s="12" t="str"/>
       <x:c r="E95" s="12" t="str"/>
       <x:c r="F95" s="12" t="str"/>
-      <x:c r="G95" s="12" t="str"/>
+      <x:c r="G95" s="14" t="str"/>
       <x:c r="H95" s="14" t="str"/>
-      <x:c r="I95" s="14" t="str"/>
-      <x:c r="J95" s="16" t="str"/>
-      <x:c r="K95" s="12" t="str"/>
-      <x:c r="L95" s="22" t="str"/>
+      <x:c r="I95" s="16" t="str"/>
+      <x:c r="J95" s="12" t="str"/>
+      <x:c r="K95" s="22" t="str"/>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="21" t="str"/>
@@ -1727,12 +1629,11 @@
       <x:c r="D96" s="12" t="str"/>
       <x:c r="E96" s="12" t="str"/>
       <x:c r="F96" s="12" t="str"/>
-      <x:c r="G96" s="12" t="str"/>
+      <x:c r="G96" s="14" t="str"/>
       <x:c r="H96" s="14" t="str"/>
-      <x:c r="I96" s="14" t="str"/>
-      <x:c r="J96" s="16" t="str"/>
-      <x:c r="K96" s="12" t="str"/>
-      <x:c r="L96" s="22" t="str"/>
+      <x:c r="I96" s="16" t="str"/>
+      <x:c r="J96" s="12" t="str"/>
+      <x:c r="K96" s="22" t="str"/>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="21" t="str"/>
@@ -1741,12 +1642,11 @@
       <x:c r="D97" s="12" t="str"/>
       <x:c r="E97" s="12" t="str"/>
       <x:c r="F97" s="12" t="str"/>
-      <x:c r="G97" s="12" t="str"/>
+      <x:c r="G97" s="14" t="str"/>
       <x:c r="H97" s="14" t="str"/>
-      <x:c r="I97" s="14" t="str"/>
-      <x:c r="J97" s="16" t="str"/>
-      <x:c r="K97" s="12" t="str"/>
-      <x:c r="L97" s="22" t="str"/>
+      <x:c r="I97" s="16" t="str"/>
+      <x:c r="J97" s="12" t="str"/>
+      <x:c r="K97" s="22" t="str"/>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="21" t="str"/>
@@ -1755,12 +1655,11 @@
       <x:c r="D98" s="12" t="str"/>
       <x:c r="E98" s="12" t="str"/>
       <x:c r="F98" s="12" t="str"/>
-      <x:c r="G98" s="12" t="str"/>
+      <x:c r="G98" s="14" t="str"/>
       <x:c r="H98" s="14" t="str"/>
-      <x:c r="I98" s="14" t="str"/>
-      <x:c r="J98" s="16" t="str"/>
-      <x:c r="K98" s="12" t="str"/>
-      <x:c r="L98" s="22" t="str"/>
+      <x:c r="I98" s="16" t="str"/>
+      <x:c r="J98" s="12" t="str"/>
+      <x:c r="K98" s="22" t="str"/>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="21" t="str"/>
@@ -1769,12 +1668,11 @@
       <x:c r="D99" s="12" t="str"/>
       <x:c r="E99" s="12" t="str"/>
       <x:c r="F99" s="12" t="str"/>
-      <x:c r="G99" s="12" t="str"/>
+      <x:c r="G99" s="14" t="str"/>
       <x:c r="H99" s="14" t="str"/>
-      <x:c r="I99" s="14" t="str"/>
-      <x:c r="J99" s="16" t="str"/>
-      <x:c r="K99" s="12" t="str"/>
-      <x:c r="L99" s="22" t="str"/>
+      <x:c r="I99" s="16" t="str"/>
+      <x:c r="J99" s="12" t="str"/>
+      <x:c r="K99" s="22" t="str"/>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="21" t="str"/>
@@ -1783,12 +1681,11 @@
       <x:c r="D100" s="12" t="str"/>
       <x:c r="E100" s="12" t="str"/>
       <x:c r="F100" s="12" t="str"/>
-      <x:c r="G100" s="12" t="str"/>
+      <x:c r="G100" s="14" t="str"/>
       <x:c r="H100" s="14" t="str"/>
-      <x:c r="I100" s="14" t="str"/>
-      <x:c r="J100" s="16" t="str"/>
-      <x:c r="K100" s="12" t="str"/>
-      <x:c r="L100" s="22" t="str"/>
+      <x:c r="I100" s="16" t="str"/>
+      <x:c r="J100" s="12" t="str"/>
+      <x:c r="K100" s="22" t="str"/>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="23" t="str"/>
@@ -1797,16 +1694,15 @@
       <x:c r="D101" s="24" t="str"/>
       <x:c r="E101" s="24" t="str"/>
       <x:c r="F101" s="24" t="str"/>
-      <x:c r="G101" s="24" t="str"/>
+      <x:c r="G101" s="25" t="str"/>
       <x:c r="H101" s="25" t="str"/>
-      <x:c r="I101" s="25" t="str"/>
-      <x:c r="J101" s="26" t="str"/>
-      <x:c r="K101" s="24" t="str"/>
-      <x:c r="L101" s="27" t="str"/>
+      <x:c r="I101" s="26" t="str"/>
+      <x:c r="J101" s="24" t="str"/>
+      <x:c r="K101" s="27" t="str"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="K2:K500">
+    <x:dataValidation type="list" sqref="J2:J101">
       <x:formula1>"MXN,USD,EUR"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
